--- a/Groceryapptesting/src/test/resources/SampleTestdata.xlsx
+++ b/Groceryapptesting/src/test/resources/SampleTestdata.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
     <sheet name="NewsPage" sheetId="2" r:id="rId2"/>
     <sheet name="AdminPage" sheetId="3" r:id="rId3"/>
     <sheet name="CategoryPage" sheetId="4" r:id="rId4"/>
+    <sheet name="FooterPage" sheetId="5" r:id="rId5"/>
+    <sheet name="ContactsPage" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>admin456</t>
+  </si>
+  <si>
+    <t>admin444</t>
+  </si>
+  <si>
+    <t>admin999</t>
+  </si>
+  <si>
+    <t>newstextarea</t>
+  </si>
+  <si>
+    <t>Schools will reopen tomorrow</t>
+  </si>
   <si>
     <t>Username1</t>
   </si>
@@ -38,37 +67,10 @@
     <t>Password1</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>admin123</t>
-  </si>
-  <si>
-    <t>admin456</t>
-  </si>
-  <si>
-    <t>admin444</t>
-  </si>
-  <si>
-    <t>admin999</t>
-  </si>
-  <si>
-    <t>newstextarea1</t>
-  </si>
-  <si>
-    <t>Schools will reopen tomorrow</t>
-  </si>
-  <si>
-    <t>Username2</t>
-  </si>
-  <si>
-    <t>Password2</t>
-  </si>
-  <si>
     <t>Dropdown</t>
   </si>
   <si>
-    <t>Irinav</t>
+    <t>Roopa</t>
   </si>
   <si>
     <t>Iri!!!234</t>
@@ -81,17 +83,48 @@
   </si>
   <si>
     <t>Sunset</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Abc,Town,NorthAmerica</t>
+  </si>
+  <si>
+    <t>xyz@yahoo.com</t>
+  </si>
+  <si>
+    <t>1231234124124</t>
+  </si>
+  <si>
+    <t>DeliveryTime</t>
+  </si>
+  <si>
+    <t>DeliveryLimit</t>
+  </si>
+  <si>
+    <t>gsdgsg@gmail.com</t>
+  </si>
+  <si>
+    <t>Banglore</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -99,6 +132,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -119,14 +160,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -569,28 +602,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,10 +747,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1200,43 +1237,43 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" customHeight="1" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1256,7 +1293,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1279,13 +1316,14 @@
   <cols>
     <col min="1" max="1" width="12.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="13.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="24.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
@@ -1332,4 +1370,100 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="19.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="15.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" ht="13.8" spans="1:3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="xyz@yahoo.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="14.2222222222222"/>
+    <col min="2" max="2" width="18.4444444444444" customWidth="1"/>
+    <col min="4" max="5" width="13.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" ht="13.8" spans="1:5">
+      <c r="A2" s="1">
+        <v>423345678</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1">
+        <v>11.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="gsdgsg@gmail.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>